--- a/审核导出/water_varnish_matte_审核.xlsx
+++ b/审核导出/water_varnish_matte_审核.xlsx
@@ -837,7 +837,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>白面牛咭M1F125、SKF125白面牛咭防彎翹使用</t>
+          <t>白麪牛咭M1F125、SKF125白麪牛咭防彎翹使用</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>白面牛咭M1F125、SKF125白面牛咭防彎翹使用</t>
+          <t>白麪牛咭M1F125、SKF125白麪牛咭防彎翹使用</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1814,12 +1814,12 @@
       </c>
       <c r="V1" s="3" t="inlineStr">
         <is>
-          <t>立体燙金</t>
+          <t>立體擊凸</t>
         </is>
       </c>
       <c r="W1" s="3" t="inlineStr">
         <is>
-          <t>立體擊凸</t>
+          <t>立體燙金</t>
         </is>
       </c>
       <c r="X1" s="3" t="inlineStr">
